--- a/Rescatables20241.xlsx
+++ b/Rescatables20241.xlsx
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="442">
   <si>
     <t>Num_Cont</t>
   </si>
@@ -1116,15 +1116,9 @@
     <t>NIETO</t>
   </si>
   <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
     <t>CHACON</t>
   </si>
   <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
     <t>PANIAGUA</t>
   </si>
   <si>
@@ -1146,15 +1140,9 @@
     <t>JESUS DAMIAN</t>
   </si>
   <si>
-    <t>HEIDI ABRIL</t>
-  </si>
-  <si>
     <t>GABRIEL URYEL</t>
   </si>
   <si>
-    <t>MARTIN ERNESTO</t>
-  </si>
-  <si>
     <t>BRYAN</t>
   </si>
   <si>
@@ -1188,94 +1176,88 @@
     <t>LEONEL</t>
   </si>
   <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>Pensamiento matemático III</t>
+  </si>
+  <si>
+    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>JHON STEVE</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>CANDELARIO</t>
+  </si>
+  <si>
+    <t>VALERIO</t>
+  </si>
+  <si>
+    <t>DIEGO DE JESUS</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
+  </si>
+  <si>
+    <t>OSCAR ALEXANDER</t>
+  </si>
+  <si>
+    <t>GESTIONA EL PROCESO DE RECLUTAMIENTO, SELECCIÓN Y ADMISIÓN DEL TALENTO HUMANO</t>
+  </si>
+  <si>
     <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>ANGEL CHARBEL</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>NATANAHEL</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>JUAN RAMON</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>SABDY</t>
-  </si>
-  <si>
-    <t>SERGIO JOSUE</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS GENERADORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>Pensamiento matemático III</t>
-  </si>
-  <si>
-    <t>MANTIENE LOS MOTORES DE CA Y CC</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>JHON STEVE</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>CANDELARIO</t>
-  </si>
-  <si>
-    <t>VALERIO</t>
-  </si>
-  <si>
-    <t>DIEGO DE JESUS</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
-  </si>
-  <si>
-    <t>OSCAR ALEXANDER</t>
-  </si>
-  <si>
-    <t>GESTIONA EL PROCESO DE RECLUTAMIENTO, SELECCIÓN Y ADMISIÓN DEL TALENTO HUMANO</t>
   </si>
   <si>
     <t>MARCO</t>
@@ -3784,7 +3766,7 @@
         <v>285</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -3804,7 +3786,7 @@
         <v>285</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -3884,7 +3866,7 @@
         <v>287</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -3904,7 +3886,7 @@
         <v>287</v>
       </c>
       <c r="E8" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -3924,7 +3906,7 @@
         <v>288</v>
       </c>
       <c r="E9" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -3944,7 +3926,7 @@
         <v>288</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -4144,7 +4126,7 @@
         <v>295</v>
       </c>
       <c r="E20" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -4164,7 +4146,7 @@
         <v>295</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -4204,7 +4186,7 @@
         <v>296</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -4224,7 +4206,7 @@
         <v>296</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -4244,7 +4226,7 @@
         <v>296</v>
       </c>
       <c r="E25" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -4284,7 +4266,7 @@
         <v>298</v>
       </c>
       <c r="E27" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -4304,7 +4286,7 @@
         <v>298</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -4824,7 +4806,7 @@
         <v>321</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4844,7 +4826,7 @@
         <v>321</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -5004,7 +4986,7 @@
         <v>328</v>
       </c>
       <c r="E13" t="s">
-        <v>124</v>
+        <v>41</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5024,7 +5006,7 @@
         <v>328</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>124</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -5064,7 +5046,7 @@
         <v>329</v>
       </c>
       <c r="E16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5084,7 +5066,7 @@
         <v>329</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="F17">
         <v>5</v>
@@ -5104,7 +5086,7 @@
         <v>329</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -5264,7 +5246,7 @@
         <v>334</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -5284,7 +5266,7 @@
         <v>334</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -5304,7 +5286,7 @@
         <v>334</v>
       </c>
       <c r="E28" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -5514,7 +5496,7 @@
         <v>346</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5534,7 +5516,7 @@
         <v>346</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5554,7 +5536,7 @@
         <v>346</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -5594,7 +5576,7 @@
         <v>348</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -5634,7 +5616,7 @@
         <v>348</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -5654,7 +5636,7 @@
         <v>349</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -5674,7 +5656,7 @@
         <v>349</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -5694,7 +5676,7 @@
         <v>349</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -5734,7 +5716,7 @@
         <v>350</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -5754,7 +5736,7 @@
         <v>350</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -5787,7 +5769,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -5821,7 +5803,7 @@
         <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E2" t="s">
         <v>70</v>
@@ -5841,10 +5823,10 @@
         <v>354</v>
       </c>
       <c r="D3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -5861,10 +5843,10 @@
         <v>354</v>
       </c>
       <c r="D4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5881,7 +5863,7 @@
         <v>354</v>
       </c>
       <c r="D5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E5" t="s">
         <v>39</v>
@@ -5901,7 +5883,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E6" t="s">
         <v>70</v>
@@ -5921,10 +5903,10 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5941,10 +5923,10 @@
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -5961,7 +5943,7 @@
         <v>355</v>
       </c>
       <c r="D9" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E9" t="s">
         <v>41</v>
@@ -5981,7 +5963,7 @@
         <v>355</v>
       </c>
       <c r="D10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E10" t="s">
         <v>39</v>
@@ -6001,7 +5983,7 @@
         <v>355</v>
       </c>
       <c r="D11" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E11" t="s">
         <v>70</v>
@@ -6021,7 +6003,7 @@
         <v>355</v>
       </c>
       <c r="D12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E12" t="s">
         <v>124</v>
@@ -6032,19 +6014,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>24330051920262</v>
+        <v>24330051920267</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>351</v>
       </c>
       <c r="C13" t="s">
         <v>356</v>
       </c>
       <c r="D13" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6052,19 +6034,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>24330051920267</v>
+        <v>24330051920274</v>
       </c>
       <c r="B14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C14" t="s">
-        <v>357</v>
+        <v>301</v>
       </c>
       <c r="D14" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E14" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6072,19 +6054,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>24330051920267</v>
+        <v>24330051920369</v>
       </c>
       <c r="B15" t="s">
-        <v>351</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>357</v>
+        <v>244</v>
       </c>
       <c r="D15" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6092,19 +6074,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>24330051920270</v>
+        <v>24330051920369</v>
       </c>
       <c r="B16" t="s">
         <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>358</v>
+        <v>244</v>
       </c>
       <c r="D16" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -6112,16 +6094,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>24330051920274</v>
+        <v>24330051920369</v>
       </c>
       <c r="B17" t="s">
-        <v>352</v>
+        <v>46</v>
       </c>
       <c r="C17" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="D17" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E17" t="s">
         <v>70</v>
@@ -6132,19 +6114,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>24330051920369</v>
+        <v>24330051920390</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -6152,19 +6134,19 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>24330051920369</v>
+        <v>24330051920390</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>244</v>
+        <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -6172,19 +6154,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>24330051920369</v>
+        <v>24330051920390</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>244</v>
+        <v>8</v>
       </c>
       <c r="D20" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="F20">
         <v>5</v>
@@ -6192,16 +6174,16 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>24330051920390</v>
+        <v>24330051920405</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>357</v>
       </c>
       <c r="D21" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E21" t="s">
         <v>39</v>
@@ -6212,19 +6194,19 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>24330051920390</v>
+        <v>24330051920405</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>357</v>
       </c>
       <c r="D22" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="F22">
         <v>5</v>
@@ -6232,19 +6214,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>24330051920390</v>
+        <v>24330051920405</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>357</v>
       </c>
       <c r="D23" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F23">
         <v>5</v>
@@ -6252,19 +6234,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>24330051920405</v>
+        <v>24330051920407</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="C24" t="s">
-        <v>359</v>
+        <v>87</v>
       </c>
       <c r="D24" t="s">
-        <v>372</v>
+        <v>232</v>
       </c>
       <c r="E24" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -6272,19 +6254,19 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>24330051920405</v>
+        <v>24330051920407</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="C25" t="s">
-        <v>359</v>
+        <v>87</v>
       </c>
       <c r="D25" t="s">
-        <v>372</v>
+        <v>232</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -6292,19 +6274,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>24330051920405</v>
+        <v>24330051920407</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="C26" t="s">
-        <v>359</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>372</v>
+        <v>232</v>
       </c>
       <c r="E26" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="F26">
         <v>5</v>
@@ -6332,19 +6314,19 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>24330051920407</v>
+        <v>24330051920409</v>
       </c>
       <c r="B28" t="s">
-        <v>353</v>
+        <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>358</v>
       </c>
       <c r="D28" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -6352,16 +6334,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>24330051920407</v>
+        <v>24330051920409</v>
       </c>
       <c r="B29" t="s">
-        <v>353</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>358</v>
       </c>
       <c r="D29" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="E29" t="s">
         <v>70</v>
@@ -6372,81 +6354,21 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>24330051920407</v>
+        <v>24330051920409</v>
       </c>
       <c r="B30" t="s">
-        <v>353</v>
+        <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>358</v>
       </c>
       <c r="D30" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>24330051920409</v>
-      </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" t="s">
-        <v>360</v>
-      </c>
-      <c r="D31" t="s">
-        <v>255</v>
-      </c>
-      <c r="E31" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>24330051920409</v>
-      </c>
-      <c r="B32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" t="s">
-        <v>360</v>
-      </c>
-      <c r="D32" t="s">
-        <v>255</v>
-      </c>
-      <c r="E32" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>24330051920409</v>
-      </c>
-      <c r="B33" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" t="s">
-        <v>360</v>
-      </c>
-      <c r="D33" t="s">
-        <v>255</v>
-      </c>
-      <c r="E33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F33">
         <v>5</v>
       </c>
     </row>
@@ -6491,7 +6413,7 @@
         <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E2" t="s">
         <v>39</v>
@@ -6508,10 +6430,10 @@
         <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="D3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E3" t="s">
         <v>38</v>
@@ -6531,10 +6453,10 @@
         <v>278</v>
       </c>
       <c r="D4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6551,10 +6473,10 @@
         <v>278</v>
       </c>
       <c r="D5" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -6568,13 +6490,13 @@
         <v>87</v>
       </c>
       <c r="C6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D6" t="s">
         <v>374</v>
       </c>
-      <c r="D6" t="s">
-        <v>378</v>
-      </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6588,10 +6510,10 @@
         <v>87</v>
       </c>
       <c r="C7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D7" t="s">
         <v>374</v>
-      </c>
-      <c r="D7" t="s">
-        <v>378</v>
       </c>
       <c r="E7" t="s">
         <v>39</v>
@@ -6608,13 +6530,13 @@
         <v>87</v>
       </c>
       <c r="C8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D8" t="s">
         <v>374</v>
       </c>
-      <c r="D8" t="s">
-        <v>378</v>
-      </c>
       <c r="E8" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6631,7 +6553,7 @@
         <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E9" t="s">
         <v>70</v>
@@ -6647,7 +6569,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -6678,10 +6600,10 @@
         <v>172</v>
       </c>
       <c r="C2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D2" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="E2" t="s">
         <v>180</v>
@@ -6698,13 +6620,13 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D3" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E3" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -6718,13 +6640,13 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E4" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -6738,10 +6660,10 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D5" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E5" t="s">
         <v>181</v>
@@ -6761,10 +6683,10 @@
         <v>182</v>
       </c>
       <c r="D6" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E6" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -6778,13 +6700,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D7" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E7" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -6792,19 +6714,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>23330051920189</v>
+        <v>23330051920195</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D8" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E8" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -6812,19 +6734,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>23330051920192</v>
+        <v>23330051920195</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
-        <v>242</v>
+        <v>379</v>
       </c>
       <c r="D9" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E9" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="F9">
         <v>5</v>
@@ -6838,13 +6760,13 @@
         <v>244</v>
       </c>
       <c r="C10" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="D10" t="s">
+        <v>386</v>
+      </c>
+      <c r="E10" t="s">
         <v>392</v>
-      </c>
-      <c r="E10" t="s">
-        <v>398</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -6852,19 +6774,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>23330051920195</v>
+        <v>23330051920203</v>
       </c>
       <c r="B11" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>384</v>
+        <v>197</v>
       </c>
       <c r="D11" t="s">
+        <v>387</v>
+      </c>
+      <c r="E11" t="s">
         <v>392</v>
-      </c>
-      <c r="E11" t="s">
-        <v>400</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -6872,19 +6794,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>23330051920195</v>
+        <v>23330051920211</v>
       </c>
       <c r="B12" t="s">
-        <v>244</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D12" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E12" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F12">
         <v>5</v>
@@ -6892,19 +6814,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>23330051920201</v>
+        <v>23330051920329</v>
       </c>
       <c r="B13" t="s">
-        <v>380</v>
+        <v>278</v>
       </c>
       <c r="C13" t="s">
-        <v>197</v>
+        <v>381</v>
       </c>
       <c r="D13" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E13" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="F13">
         <v>5</v>
@@ -6912,19 +6834,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>23330051920203</v>
+        <v>23330051920332</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="D14" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="E14" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -6932,19 +6854,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>23330051920211</v>
+        <v>23330051920332</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>385</v>
+        <v>222</v>
       </c>
       <c r="D15" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E15" t="s">
-        <v>398</v>
+        <v>192</v>
       </c>
       <c r="F15">
         <v>5</v>
@@ -6952,81 +6874,21 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>23330051920329</v>
+        <v>23330051920332</v>
       </c>
       <c r="B16" t="s">
-        <v>278</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>386</v>
+        <v>222</v>
       </c>
       <c r="D16" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="E16" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="F16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>23330051920332</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>222</v>
-      </c>
-      <c r="D17" t="s">
-        <v>397</v>
-      </c>
-      <c r="E17" t="s">
-        <v>398</v>
-      </c>
-      <c r="F17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>23330051920332</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>222</v>
-      </c>
-      <c r="D18" t="s">
-        <v>397</v>
-      </c>
-      <c r="E18" t="s">
-        <v>192</v>
-      </c>
-      <c r="F18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>23330051920332</v>
-      </c>
-      <c r="B19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" t="s">
-        <v>222</v>
-      </c>
-      <c r="D19" t="s">
-        <v>397</v>
-      </c>
-      <c r="E19" t="s">
-        <v>399</v>
-      </c>
-      <c r="F19">
         <v>5</v>
       </c>
     </row>
@@ -7068,13 +6930,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D2" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="E2" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -7088,10 +6950,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D3" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="E3" t="s">
         <v>179</v>
@@ -7108,10 +6970,10 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D4" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="E4" t="s">
         <v>192</v>
@@ -7188,10 +7050,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="D2" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="E2" t="s">
         <v>181</v>
@@ -7208,10 +7070,10 @@
         <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="D3" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="E3" t="s">
         <v>180</v>
@@ -7228,13 +7090,13 @@
         <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="D4" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="E4" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -7248,13 +7110,13 @@
         <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="D5" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="E5" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -7268,10 +7130,10 @@
         <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="D6" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="E6" t="s">
         <v>192</v>
@@ -7345,13 +7207,13 @@
         <v>22330051920177</v>
       </c>
       <c r="B2" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C2" t="s">
         <v>338</v>
       </c>
       <c r="D2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E2" t="s">
         <v>211</v>
@@ -7388,10 +7250,10 @@
         <v>278</v>
       </c>
       <c r="C4" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="D4" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E4" t="s">
         <v>211</v>
@@ -7411,7 +7273,7 @@
         <v>197</v>
       </c>
       <c r="D5" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E5" t="s">
         <v>211</v>
@@ -7431,7 +7293,7 @@
         <v>225</v>
       </c>
       <c r="D6" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E6" t="s">
         <v>212</v>
@@ -7451,10 +7313,10 @@
         <v>225</v>
       </c>
       <c r="D7" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="E7" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -7465,16 +7327,16 @@
         <v>22330051920359</v>
       </c>
       <c r="B8" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="C8" t="s">
         <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E8" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -8051,10 +7913,10 @@
         <v>195</v>
       </c>
       <c r="D2" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="E2" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="F2">
         <v>5</v>
@@ -8071,10 +7933,10 @@
         <v>195</v>
       </c>
       <c r="D3" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="E3" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="F3">
         <v>5</v>
@@ -8085,13 +7947,13 @@
         <v>22330051920401</v>
       </c>
       <c r="B4" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C4" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D4" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E4" t="s">
         <v>212</v>
@@ -8141,7 +8003,7 @@
         <v>128</v>
       </c>
       <c r="D2" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E2" t="s">
         <v>212</v>
@@ -8155,13 +8017,13 @@
         <v>21330051920396</v>
       </c>
       <c r="B3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C3" t="s">
         <v>217</v>
       </c>
       <c r="D3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E3" t="s">
         <v>212</v>
@@ -8178,10 +8040,10 @@
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D4" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E4" t="s">
         <v>212</v>
@@ -8198,10 +8060,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D5" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E5" t="s">
         <v>212</v>
@@ -8221,7 +8083,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E6" t="s">
         <v>212</v>
@@ -8265,13 +8127,13 @@
         <v>22330051920205</v>
       </c>
       <c r="B2" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C2" t="s">
         <v>305</v>
       </c>
       <c r="D2" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="E2" t="s">
         <v>212</v>
@@ -8288,10 +8150,10 @@
         <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D3" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="E3" t="s">
         <v>212</v>
@@ -8305,13 +8167,13 @@
         <v>22330051920225</v>
       </c>
       <c r="B4" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C4" t="s">
         <v>309</v>
       </c>
       <c r="D4" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E4" t="s">
         <v>211</v>
@@ -8325,13 +8187,13 @@
         <v>22330051920225</v>
       </c>
       <c r="B5" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C5" t="s">
         <v>309</v>
       </c>
       <c r="D5" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E5" t="s">
         <v>236</v>
@@ -8345,13 +8207,13 @@
         <v>22330051920225</v>
       </c>
       <c r="B6" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C6" t="s">
         <v>309</v>
       </c>
       <c r="D6" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E6" t="s">
         <v>209</v>
@@ -8365,16 +8227,16 @@
         <v>22330051920225</v>
       </c>
       <c r="B7" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C7" t="s">
         <v>309</v>
       </c>
       <c r="D7" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E7" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F7">
         <v>-1</v>
@@ -8388,10 +8250,10 @@
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="D8" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="E8" t="s">
         <v>212</v>
@@ -8408,10 +8270,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D9" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E9" t="s">
         <v>212</v>
@@ -8458,10 +8320,10 @@
         <v>196</v>
       </c>
       <c r="C2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D2" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E2" t="s">
         <v>236</v>
@@ -8478,13 +8340,13 @@
         <v>196</v>
       </c>
       <c r="C3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D3" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E3" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="F3">
         <v>-1</v>
@@ -8498,10 +8360,10 @@
         <v>196</v>
       </c>
       <c r="C4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D4" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E4" t="s">
         <v>209</v>
@@ -8518,10 +8380,10 @@
         <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D5" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="E5" t="s">
         <v>211</v>
@@ -8541,7 +8403,7 @@
         <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E6" t="s">
         <v>209</v>
@@ -8561,7 +8423,7 @@
         <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E7" t="s">
         <v>211</v>
@@ -8581,7 +8443,7 @@
         <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E8" t="s">
         <v>236</v>
@@ -8601,10 +8463,10 @@
         <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E9" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -8615,13 +8477,13 @@
         <v>22330051920309</v>
       </c>
       <c r="B10" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="E10" t="s">
         <v>236</v>
@@ -8635,13 +8497,13 @@
         <v>22330051920309</v>
       </c>
       <c r="B11" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="E11" t="s">
         <v>209</v>
@@ -8655,16 +8517,16 @@
         <v>22330051920309</v>
       </c>
       <c r="B12" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C12" t="s">
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="E12" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="F12">
         <v>-1</v>
@@ -8675,13 +8537,13 @@
         <v>22330051920309</v>
       </c>
       <c r="B13" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="E13" t="s">
         <v>211</v>
@@ -8698,13 +8560,13 @@
         <v>169</v>
       </c>
       <c r="C14" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D14" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E14" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="F14">
         <v>-1</v>
@@ -8718,10 +8580,10 @@
         <v>169</v>
       </c>
       <c r="C15" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D15" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E15" t="s">
         <v>211</v>
@@ -8738,10 +8600,10 @@
         <v>169</v>
       </c>
       <c r="C16" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D16" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E16" t="s">
         <v>236</v>
@@ -8758,10 +8620,10 @@
         <v>169</v>
       </c>
       <c r="C17" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="D17" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E17" t="s">
         <v>209</v>
